--- a/T3_New/SO TIEN HOAN THANH - BC KPMMMK.xlsx
+++ b/T3_New/SO TIEN HOAN THANH - BC KPMMMK.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code_cokhi\Bao_Cao_MMK_KPI\T3_New\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20306AC-115D-4468-8CD9-87756169E4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89BF31B8-5351-4771-9DA4-6B2424B45416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="So_tien_HT" sheetId="1" r:id="rId1"/>
@@ -482,15 +482,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="1"/>
-    <col min="2" max="2" width="28.44140625" style="1" customWidth="1"/>
-    <col min="3" max="14" width="14.88671875" style="4" customWidth="1"/>
-    <col min="15" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="28.42578125" style="1" customWidth="1"/>
+    <col min="3" max="14" width="14.85546875" style="4" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="9"/>
       <c r="B1" s="10" t="s">
         <v>0</v>
@@ -508,7 +508,7 @@
       <c r="M1" s="10"/>
       <c r="N1" s="10"/>
     </row>
-    <row r="2" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -549,7 +549,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
@@ -558,7 +558,9 @@
       <c r="E3" s="6">
         <v>3033488725</v>
       </c>
-      <c r="F3" s="6"/>
+      <c r="F3" s="6">
+        <v>111545680</v>
+      </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
@@ -568,7 +570,7 @@
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
@@ -587,7 +589,7 @@
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
         <v>15</v>
       </c>
